--- a/data/eventos.xlsx
+++ b/data/eventos.xlsx
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SI marca automáticamente como cerrados los lunes que no tengan partido ni evento manual.</t>
+          <t>SI marca todos los lunes como cerrados aunque haya partido. Solo un evento manual en este Excel abre ese lunes.</t>
         </is>
       </c>
     </row>
